--- a/output_tcc_var/tabelas/01_testes_F_granger.xlsx
+++ b/output_tcc_var/tabelas/01_testes_F_granger.xlsx
@@ -455,14 +455,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.455683261711882</v>
+        <v>0.709996918652676</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2337407427082264</v>
+        <v>0.5851656979073758</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(2, 988)</t>
+          <t>(4, 948)</t>
         </is>
       </c>
     </row>
@@ -478,14 +478,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6921140132923499</v>
+        <v>1.242530786907214</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5007593534221711</v>
+        <v>0.2911810325013763</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(2, 988)</t>
+          <t>(4, 948)</t>
         </is>
       </c>
     </row>
@@ -501,14 +501,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2974860254139461</v>
+        <v>0.8807431725246488</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7427494623162865</v>
+        <v>0.4748212620435377</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(2, 988)</t>
+          <t>(4, 948)</t>
         </is>
       </c>
     </row>
@@ -524,14 +524,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.136549992700123</v>
+        <v>1.020090470473152</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3377887054865273</v>
+        <v>0.4188155593058407</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(4, 988)</t>
+          <t>(8, 948)</t>
         </is>
       </c>
     </row>
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.518629590650312</v>
+        <v>2.515937957644651</v>
       </c>
       <c r="D6" t="n">
-        <v>0.112821938532309</v>
+        <v>0.1130141904841546</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.414362655139881</v>
+        <v>2.413422703648515</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1205407894187633</v>
+        <v>0.1206129808955529</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1741134356854259</v>
+        <v>0.1743479070065849</v>
       </c>
       <c r="D8" t="n">
-        <v>0.676570499020391</v>
+        <v>0.6763651645621508</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.262749198675036</v>
+        <v>1.261443498450873</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2833223579834372</v>
+        <v>0.283691608400703</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.340369284490427</v>
+        <v>2.33762349807301</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1263734092530222</v>
+        <v>0.1265958082780679</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.311847425658387</v>
+        <v>2.310837174723897</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1287049739173688</v>
+        <v>0.1287884332854729</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002013742065877593</v>
+        <v>0.002037058723035909</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9642160411031017</v>
+        <v>0.9640096101817549</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.175896984354444</v>
+        <v>1.17448569538716</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3089649760427435</v>
+        <v>0.3094003069478446</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.038902913130522</v>
+        <v>2.036326861301817</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1536299264993201</v>
+        <v>0.1538897878102742</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.163659202318749</v>
+        <v>2.162706380175677</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1416199188203252</v>
+        <v>0.1417075333678434</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.3055303839089875</v>
+        <v>0.3054479230021214</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5805585115537644</v>
+        <v>0.5806095809458089</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.329070368181194</v>
+        <v>1.327603983911363</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2651867367664446</v>
+        <v>0.2655748639841924</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.00294446336154</v>
+        <v>0.9702810147093255</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3671709541326871</v>
+        <v>0.379337343732555</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.234109954144963</v>
+        <v>1.224552316342281</v>
       </c>
       <c r="D19" t="n">
-        <v>0.291542061288764</v>
+        <v>0.2943348899072247</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6077666841478697</v>
+        <v>0.5838152564869278</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5447691653997414</v>
+        <v>0.5579585803979376</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.019363171083875</v>
+        <v>1.007249377552127</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3961930010239079</v>
+        <v>0.4026503915860977</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.245259725720551</v>
+        <v>1.245259725720757</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2883175354796427</v>
+        <v>0.2883175354795835</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.262467900228011</v>
+        <v>1.262467900228022</v>
       </c>
       <c r="D23" t="n">
-        <v>0.283410908762557</v>
+        <v>0.2834109087625539</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.134822032465126</v>
+        <v>1.13482203246501</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3218979971518491</v>
+        <v>0.3218979971518864</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.285929313185064</v>
+        <v>1.285929313185153</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2736686849450908</v>
+        <v>0.2736686849450592</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.417823850519095</v>
+        <v>4.417823850519661</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03581302342443503</v>
+        <v>0.03581302342442319</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.285112779319003</v>
+        <v>1.285112779319062</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2572201010735112</v>
+        <v>0.2572201010735001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1303290562535776</v>
+        <v>0.1303290562536837</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7181667516144905</v>
+        <v>0.7181667516143807</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.285156833154276</v>
+        <v>2.285156833154622</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1022850309875629</v>
+        <v>0.1022850309875276</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.681878934805247</v>
+        <v>4.681878934805841</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03071674174447418</v>
+        <v>0.0307167417444636</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.343124435199613</v>
+        <v>1.343124435199611</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2467581928241857</v>
+        <v>0.246758192824186</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.4075480881710453</v>
+        <v>0.4075480881708936</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5233616396078874</v>
+        <v>0.5233616396079647</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.426207245930054</v>
+        <v>2.426207245930289</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08888728643634899</v>
+        <v>0.08888728643632823</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
